--- a/data/trans_orig/Q47-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su talla</t>
+          <t>Población según su talla (tasa de respuesta: 98,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>172,0; 173,14</t>
+          <t>171,99; 173,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>171,74; 172,94</t>
+          <t>171,73; 172,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172,38; 173,59</t>
+          <t>172,41; 173,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172,68; 174,09</t>
+          <t>172,75; 174,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>160,07; 161,06</t>
+          <t>160,04; 161,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>160,07; 161,17</t>
+          <t>160,05; 161,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>160,22; 161,28</t>
+          <t>160,17; 161,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>161,48; 162,32</t>
+          <t>161,44; 162,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>166,1; 167,05</t>
+          <t>166,11; 167,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166,04; 167,06</t>
+          <t>166,1; 167,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166,45; 167,49</t>
+          <t>166,4; 167,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>166,97; 168,14</t>
+          <t>166,99; 168,08</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>172,81; 173,75</t>
+          <t>172,75; 173,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>172,49; 173,47</t>
+          <t>172,51; 173,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173,09; 174,08</t>
+          <t>173,06; 174,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173,72; 178,34</t>
+          <t>173,75; 178,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>160,01; 160,9</t>
+          <t>160,02; 160,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>160,34; 161,2</t>
+          <t>160,35; 161,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>160,96; 161,82</t>
+          <t>160,92; 161,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>161,96; 162,7</t>
+          <t>161,93; 162,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>166,41; 167,27</t>
+          <t>166,37; 167,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166,48; 167,33</t>
+          <t>166,47; 167,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167,02; 167,87</t>
+          <t>167,01; 167,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>167,96; 173,17</t>
+          <t>167,95; 174,11</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>172,71; 173,88</t>
+          <t>172,73; 173,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173,02; 174,2</t>
+          <t>173,02; 174,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173,29; 174,38</t>
+          <t>173,3; 174,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172,69; 173,89</t>
+          <t>172,76; 173,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>160,73; 161,74</t>
+          <t>160,79; 161,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>160,69; 161,73</t>
+          <t>160,7; 161,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161,48; 162,47</t>
+          <t>161,52; 162,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>157,81; 162,28</t>
+          <t>157,89; 162,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>166,74; 167,74</t>
+          <t>166,75; 167,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166,81; 167,85</t>
+          <t>166,86; 167,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167,32; 168,34</t>
+          <t>167,37; 168,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>161,94; 167,95</t>
+          <t>162,27; 167,94</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>173,04; 173,92</t>
+          <t>173,01; 173,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172,96; 174,0</t>
+          <t>173,0; 174,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174,24; 175,27</t>
+          <t>174,24; 175,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173,57; 174,71</t>
+          <t>173,59; 174,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>160,88; 161,71</t>
+          <t>160,86; 161,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>161,02; 161,83</t>
+          <t>161,01; 161,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,11; 161,94</t>
+          <t>161,13; 161,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>159,5; 162,06</t>
+          <t>159,43; 162,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166,75; 167,51</t>
+          <t>166,71; 167,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,76; 167,62</t>
+          <t>166,75; 167,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167,33; 168,25</t>
+          <t>167,37; 168,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>165,5; 167,86</t>
+          <t>165,49; 167,93</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,42</t>
+          <t>172,92; 173,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172,87; 173,39</t>
+          <t>172,83; 173,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173,59; 174,13</t>
+          <t>173,58; 174,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173,64; 176,03</t>
+          <t>173,63; 176,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>160,65; 161,11</t>
+          <t>160,69; 161,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>160,78; 161,26</t>
+          <t>160,83; 161,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>161,22; 161,71</t>
+          <t>161,22; 161,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>160,25; 162,02</t>
+          <t>159,95; 162,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,18</t>
+          <t>166,72; 167,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166,78; 167,24</t>
+          <t>166,79; 167,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167,32; 167,8</t>
+          <t>167,32; 167,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>166,73; 169,32</t>
+          <t>166,77; 169,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q47-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173,33</t>
+          <t>173,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>161,88</t>
+          <t>161,96</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>167,49</t>
+          <t>167,53</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>171,99; 173,11</t>
+          <t>171,98; 173,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>171,73; 172,89</t>
+          <t>171,74; 172,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172,41; 173,62</t>
+          <t>172,38; 173,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172,75; 174,16</t>
+          <t>172,7; 173,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>160,04; 161,04</t>
+          <t>160,0; 161,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>160,05; 161,14</t>
+          <t>160,08; 161,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>160,17; 161,27</t>
+          <t>160,19; 161,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>161,44; 162,27</t>
+          <t>161,58; 162,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>166,11; 167,07</t>
+          <t>166,02; 167,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166,1; 167,12</t>
+          <t>166,09; 167,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166,4; 167,45</t>
+          <t>166,4; 167,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>166,99; 168,08</t>
+          <t>167,07; 167,99</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175,57</t>
+          <t>173,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>162,3</t>
+          <t>162,26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>169,71</t>
+          <t>168,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>172,75; 173,73</t>
+          <t>172,74; 173,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>172,51; 173,44</t>
+          <t>172,51; 173,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173,06; 174,01</t>
+          <t>173,06; 174,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173,75; 178,79</t>
+          <t>173,38; 174,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>160,02; 160,89</t>
+          <t>159,98; 160,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>160,35; 161,19</t>
+          <t>160,31; 161,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>160,92; 161,84</t>
+          <t>160,98; 161,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>161,93; 162,66</t>
+          <t>161,96; 162,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>166,37; 167,28</t>
+          <t>166,38; 167,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166,47; 167,35</t>
+          <t>166,5; 167,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167,01; 167,86</t>
+          <t>167,01; 167,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>167,95; 174,11</t>
+          <t>167,62; 168,4</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173,33</t>
+          <t>173,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>160,48</t>
+          <t>162,15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>166,16</t>
+          <t>167,81</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>172,73; 173,85</t>
+          <t>172,67; 173,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173,02; 174,18</t>
+          <t>173,0; 174,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173,3; 174,4</t>
+          <t>173,28; 174,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172,76; 173,93</t>
+          <t>172,95; 174,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>160,79; 161,77</t>
+          <t>160,72; 161,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>160,7; 161,7</t>
+          <t>160,67; 161,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161,52; 162,51</t>
+          <t>161,53; 162,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>157,89; 162,28</t>
+          <t>161,75; 162,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>166,75; 167,73</t>
+          <t>166,71; 167,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166,86; 167,88</t>
+          <t>166,84; 167,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167,37; 168,32</t>
+          <t>167,4; 168,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>162,27; 167,94</t>
+          <t>167,35; 168,3</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174,1</t>
+          <t>174,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>161,3</t>
+          <t>161,99</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>167,21</t>
+          <t>167,69</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>173,01; 173,88</t>
+          <t>173,01; 173,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>173,0; 174,01</t>
+          <t>172,97; 173,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174,24; 175,22</t>
+          <t>174,23; 175,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173,59; 174,68</t>
+          <t>173,53; 174,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>160,86; 161,63</t>
+          <t>160,9; 161,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>161,01; 161,85</t>
+          <t>161,02; 161,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,13; 161,99</t>
+          <t>161,16; 161,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>159,43; 162,05</t>
+          <t>161,65; 162,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166,71; 167,58</t>
+          <t>166,67; 167,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,75; 167,62</t>
+          <t>166,76; 167,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167,37; 168,32</t>
+          <t>167,38; 168,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>165,49; 167,93</t>
+          <t>167,29; 168,09</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174,31</t>
+          <t>173,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>161,47</t>
+          <t>162,1</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>167,79</t>
+          <t>167,78</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,44</t>
+          <t>172,91; 173,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172,83; 173,39</t>
+          <t>172,85; 173,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173,58; 174,1</t>
+          <t>173,58; 174,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173,63; 176,17</t>
+          <t>173,47; 173,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>160,69; 161,12</t>
+          <t>160,66; 161,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>160,83; 161,28</t>
+          <t>160,78; 161,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>161,22; 161,69</t>
+          <t>161,21; 161,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>159,95; 162,0</t>
+          <t>161,91; 162,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,19</t>
+          <t>166,73; 167,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167,32; 167,79</t>
+          <t>167,28; 167,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>166,77; 169,25</t>
+          <t>167,54; 168,0</t>
         </is>
       </c>
     </row>
